--- a/app/backend/2025_11_07_Friday_Sermon_KM5_120642_206380_ENG.xlsx
+++ b/app/backend/2025_11_07_Friday_Sermon_KM5_120642_206380_ENG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/m9/Documents/personal_programming/python/projects/gpt/app/backend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{276BFE0A-013E-E54B-B7FF-C460738BD7A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A656C9B1-A6D0-434E-9487-C2F8049546E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
